--- a/docs/compliance/spreadsheets/Sub_Processors.xlsx
+++ b/docs/compliance/spreadsheets/Sub_Processors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-processors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sub-processors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sub-processors'!$A$1:$H$10</definedName>
@@ -508,7 +508,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Last reviewed: 2026-08-25</t>
+          <t>Last reviewed: 2026-10-02</t>
         </is>
       </c>
     </row>
